--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98372</v>
+        <v>98374</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104072</v>
+        <v>104074</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104074</v>
+        <v>104080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
+        <v>92690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104080</v>
+        <v>104082</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92690</v>
+        <v>92691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104082</v>
+        <v>104083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92691</v>
+        <v>92697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92311</v>
+        <v>92317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104083</v>
+        <v>104089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92697</v>
+        <v>92701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92317</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104089</v>
+        <v>104093</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104093</v>
+        <v>104095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98395</v>
+        <v>98397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104095</v>
+        <v>104097</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92323</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136764259</v>
       </c>
       <c r="B39" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>136764707</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136765001</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136764697</v>
       </c>
       <c r="B42" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98397</v>
+        <v>98410</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104097</v>
+        <v>104110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136764259</v>
       </c>
       <c r="B39" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>136764707</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136765001</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136764697</v>
       </c>
       <c r="B42" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104110</v>
+        <v>104112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -4811,11 +4811,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4926,11 +4922,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5041,11 +5033,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98412</v>
+        <v>98415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104112</v>
+        <v>104115</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92341</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136764259</v>
       </c>
       <c r="B39" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>136764707</v>
       </c>
       <c r="B40" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>136765001</v>
       </c>
       <c r="B41" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>136764697</v>
       </c>
       <c r="B42" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98415</v>
+        <v>98425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104115</v>
+        <v>104130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104130</v>
+        <v>104131</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92352</v>
+        <v>92355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136764268</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136764610</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136765029</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136764294</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136764313</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136764331</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136764374</v>
       </c>
       <c r="B12" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136764428</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136764453</v>
       </c>
       <c r="B14" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136764458</v>
       </c>
       <c r="B15" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136764543</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136764553</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136764592</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136764599</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136764622</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136764651</v>
       </c>
       <c r="B21" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>136764692</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136764840</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136764851</v>
       </c>
       <c r="B24" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>136764878</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136764922</v>
       </c>
       <c r="B26" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>136764951</v>
       </c>
       <c r="B27" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>136765025</v>
       </c>
       <c r="B28" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136765026</v>
       </c>
       <c r="B29" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136764465</v>
       </c>
       <c r="B30" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>136764602</v>
       </c>
       <c r="B31" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>136764871</v>
       </c>
       <c r="B32" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136764875</v>
       </c>
       <c r="B33" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136764934</v>
       </c>
       <c r="B34" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136764341</v>
       </c>
       <c r="B35" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136764544</v>
       </c>
       <c r="B36" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>136764868</v>
       </c>
       <c r="B37" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>136764926</v>
       </c>
       <c r="B38" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136764259</v>
       </c>
       <c r="B39" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>136764707</v>
       </c>
       <c r="B40" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>136765001</v>
       </c>
       <c r="B41" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>136764697</v>
       </c>
       <c r="B42" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98426</v>
+        <v>98431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104131</v>
+        <v>104136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 36941-2026 artfynd.xlsx
+++ b/artfynd/A 36941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136765034</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136764487</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136764556</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136764490</v>
       </c>
       <c r="B5" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136764835</v>
       </c>
       <c r="B43" t="n">
-        <v>98431</v>
+        <v>98433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136764496</v>
       </c>
       <c r="B44" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>136764519</v>
       </c>
       <c r="B45" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136764583</v>
       </c>
       <c r="B46" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136764902</v>
       </c>
       <c r="B47" t="n">
-        <v>104136</v>
+        <v>104139</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
